--- a/dances.xlsx
+++ b/dances.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="165">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -85,6 +85,15 @@
     <t xml:space="preserve">Anniversary Dance!</t>
   </si>
   <si>
+    <t xml:space="preserve">Graduation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doug’s + </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
     <t xml:space="preserve">CarlaPeck.jpg</t>
   </si>
   <si>
@@ -229,9 +238,6 @@
     <t xml:space="preserve">Turkey Supper</t>
   </si>
   <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leroy Conrad</t>
   </si>
   <si>
@@ -239,6 +245,303 @@
   </si>
   <si>
     <t xml:space="preserve">chris_wildhagen.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapid8s.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just For Laughs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirates Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blooms &amp; Butterflies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stars &amp; Stripes Forever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mild, Mild West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trivia Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teepees and Tomahawks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falling Leaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanksgiving Potluck / Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa’s Socks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">circulators.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peanut Butter &amp; Jelly Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kentucky Derby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stardusters.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">St Patrick’s Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salad Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singing, Dancers’ Choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strawberry Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Cream Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AceyDuceys.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WheelSteppers.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DonSeaman.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuhle.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solosteppers.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DougSprosty.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Barbecue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popcorn Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mothers’ Day Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinco De Mayo Fiesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gospel Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fathers Day Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TomKathyNickle.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizza Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurtBraffet.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food Pantry Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root Beer Float Night</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Club 52</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">nd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Anniversary</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Baked Potato Bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sports Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halloween Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanksgiving Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toys for Tots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manning.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christmas Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Year’s Eve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circlesquareb.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brunch and Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Big Skirt Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maybe cookout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dudesdolls.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BarryJohnson.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DanPreedy.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jesseMillspaugh.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DennisThompson.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BobAsp.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvest Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tannehille.avif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PetticoatsJunction.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal following, raffle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINK-Ladies.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masquerade Ball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camo Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoessHills.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnionSquares.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Shed Dance – NOT in Creston!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanglefoot.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LeroyConrad.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supper at 6:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenny Bailey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NE District Dance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">District callers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">District cuers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon / Lime Laughter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Cream Party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trivia Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pizza Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heartland.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weaklend.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JerryJunck.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stairs.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darwin Barker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sue Dellere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brianfreed.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sullivan.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BryanBush.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ken Mai</t>
   </si>
 </sst>
 </file>
@@ -250,7 +553,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -271,6 +574,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -332,15 +642,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,7 +666,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -380,37 +690,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -483,170 +793,170 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K288"/>
+  <dimension ref="A1:K287"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="9.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="6.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="23.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="18.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="20.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="10.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="15.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="2" width="9.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="6.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="1" t="n">
         <v>46004</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="1" t="n">
         <v>46039</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="1" t="n">
         <v>46053</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="1" t="n">
         <v>46081</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="1" t="n">
         <v>46095</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="1" t="n">
         <v>46101</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="1" t="n">
         <v>46102</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="1" t="n">
         <v>46110</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="5" t="n">
@@ -657,749 +967,752 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="1" t="n">
         <v>46137</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>46151</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
+      <c r="A11" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="1" t="s">
-        <v>22</v>
+      <c r="K11" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>46214</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
+      <c r="H12" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
-        <v>46221</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
-        <v>46235</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
+      <c r="H14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
-        <v>46256</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
+      <c r="C15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
+      <c r="C16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>16</v>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
+      <c r="A18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>29</v>
+      <c r="A19" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
+      <c r="H19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>46340</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
+      <c r="A20" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
-        <v>46368</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
+      <c r="A21" s="1" t="n">
+        <v>46340</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
-        <v>46060</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="A22" s="1" t="n">
+        <v>46368</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>31</v>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
-        <v>46074</v>
+      <c r="A23" s="1" t="n">
+        <v>46060</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
-        <v>46088</v>
+      <c r="A24" s="1" t="n">
+        <v>46074</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
-        <v>46116</v>
+      <c r="A25" s="1" t="n">
+        <v>46088</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="1" t="s">
-        <v>36</v>
+      <c r="H25" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
         <v>46145</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F26" s="5" t="n">
+      <c r="B27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G27" s="6" t="n">
         <v>0.694444444444444</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="H27" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
         <v>46158</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
-        <v>46179</v>
-      </c>
       <c r="B28" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="1" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
-        <v>46214</v>
+      <c r="A29" s="1" t="n">
+        <v>46179</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="1" t="s">
-        <v>43</v>
+      <c r="H29" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="5" t="n">
+      <c r="B31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <v>0.75</v>
       </c>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
         <v>46270</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
-        <v>46284</v>
-      </c>
       <c r="B32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
+      <c r="H32" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
-        <v>46298</v>
+      <c r="A33" s="1" t="n">
+        <v>46284</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
-        <v>46333</v>
+      <c r="A34" s="1" t="n">
+        <v>46298</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
+      <c r="H34" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
-        <v>46347</v>
-      </c>
-      <c r="B35" s="4"/>
+      <c r="A35" s="1" t="n">
+        <v>46333</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="1" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
-        <v>46361</v>
+      <c r="A36" s="1" t="n">
+        <v>46347</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6"/>
-      <c r="J36" s="1" t="s">
-        <v>49</v>
+      <c r="H36" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
-        <v>46375</v>
+      <c r="A37" s="1" t="n">
+        <v>46361</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="1" t="s">
-        <v>51</v>
+      <c r="J37" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>21</v>
+      <c r="A38" s="1" t="n">
+        <v>46375</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6"/>
+      <c r="H38" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>29</v>
+      <c r="A39" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
-        <v>46136</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>11</v>
+      <c r="A40" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
-        <v>46150</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>21</v>
+      <c r="A41" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="1" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
-        <v>46075</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="A42" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
-        <v>46103</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>54</v>
+      <c r="A43" s="1" t="n">
+        <v>46075</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6"/>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
-        <v>46138</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6"/>
+      <c r="H44" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>60</v>
+      <c r="A45" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="1" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>58</v>
+      <c r="A46" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6"/>
+      <c r="H46" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>62</v>
+      <c r="A47" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="1" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
-        <v>46257</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>63</v>
+      <c r="A48" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="0"/>
+      <c r="H48" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>60</v>
+      <c r="A49" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="1" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>65</v>
+      <c r="A50" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6"/>
+      <c r="H50" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>65</v>
+      <c r="A51" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>65</v>
+      <c r="A52" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
-        <v>46320</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>66</v>
+      <c r="A53" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="1" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
-        <v>46348</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>68</v>
+      <c r="A54" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6"/>
+      <c r="H54" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="1" t="n">
+        <v>46348</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
         <v>46387</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" s="5" t="n">
+      <c r="B56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" s="5" t="n">
         <v>0.875</v>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G56" s="6" t="n">
         <v>0.00347222222222222</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
         <v>46057</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
-        <v>46085</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>58</v>
+      <c r="B57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1407,19 +1720,19 @@
       <c r="G57" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>69</v>
+      <c r="K57" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>58</v>
+      <c r="A58" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1427,16 +1740,19 @@
       <c r="G58" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>69</v>
+      <c r="K58" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="n">
-        <v>46148</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>54</v>
+      <c r="A59" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1444,22 +1760,16 @@
       <c r="G59" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>69</v>
+      <c r="K59" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>58</v>
+      <c r="A60" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F60" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1467,16 +1777,22 @@
       <c r="G60" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K60" s="1" t="s">
-        <v>69</v>
+      <c r="H60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="n">
-        <v>46204</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>54</v>
+      <c r="A61" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1484,22 +1800,16 @@
       <c r="G61" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>69</v>
+      <c r="K61" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="n">
-        <v>46239</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>58</v>
+      <c r="A62" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1507,19 +1817,22 @@
       <c r="G62" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>69</v>
+      <c r="H62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>58</v>
+      <c r="A63" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F63" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1527,16 +1840,19 @@
       <c r="G63" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>69</v>
+      <c r="K63" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>54</v>
+      <c r="A64" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1544,22 +1860,16 @@
       <c r="G64" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>69</v>
+      <c r="K64" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="n">
-        <v>46330</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>58</v>
+      <c r="A65" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1567,19 +1877,22 @@
       <c r="G65" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>69</v>
+      <c r="H65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="n">
-        <v>46358</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>72</v>
+      <c r="A66" s="1" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>0.791666666666667</v>
@@ -1587,1117 +1900,2885 @@
       <c r="G66" s="6" t="n">
         <v>0.875</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>69</v>
+      <c r="K66" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="6"/>
+      <c r="A67" s="1" t="n">
+        <v>46358</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3"/>
+      <c r="A68" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="3"/>
+      <c r="A69" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3"/>
+      <c r="A70" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3"/>
+      <c r="A71" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3"/>
+      <c r="A72" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3"/>
+      <c r="A73" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3"/>
+      <c r="A74" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="3"/>
+      <c r="A75" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="6"/>
+      <c r="A76" s="1" t="n">
+        <v>46346</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3"/>
+      <c r="A77" s="1" t="n">
+        <v>46374</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3"/>
+      <c r="A78" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="4"/>
+      <c r="E78" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="F78" s="5"/>
       <c r="G78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3"/>
+      <c r="A79" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="F79" s="5"/>
       <c r="G79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3"/>
+      <c r="A80" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="F80" s="5"/>
       <c r="G80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3"/>
+      <c r="A81" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="F81" s="5"/>
       <c r="G81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="3"/>
+      <c r="A82" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="F82" s="5"/>
       <c r="G82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3"/>
+      <c r="A83" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="F83" s="5"/>
       <c r="G83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="3"/>
+      <c r="A84" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="F84" s="5"/>
       <c r="G84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3"/>
+      <c r="A85" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="F85" s="5"/>
       <c r="G85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3"/>
+      <c r="A86" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F86" s="5"/>
       <c r="G86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3"/>
+      <c r="A87" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F87" s="5"/>
       <c r="G87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3"/>
+      <c r="A88" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F88" s="5"/>
       <c r="G88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3"/>
+      <c r="A89" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F89" s="5"/>
       <c r="G89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3"/>
+      <c r="A90" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F90" s="5"/>
       <c r="G90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3"/>
+      <c r="A91" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F91" s="5"/>
       <c r="G91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3"/>
+      <c r="A92" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F92" s="5"/>
       <c r="G92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="3"/>
+      <c r="A93" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F93" s="5"/>
       <c r="G93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3"/>
+      <c r="A94" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F94" s="5"/>
       <c r="G94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="3"/>
+      <c r="A95" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F95" s="5"/>
       <c r="G95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3"/>
+      <c r="A96" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F96" s="5"/>
       <c r="G96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="3"/>
+      <c r="A97" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F97" s="5"/>
       <c r="G97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3"/>
+      <c r="A98" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F98" s="5"/>
       <c r="G98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3"/>
+      <c r="A99" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F99" s="5"/>
       <c r="G99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3"/>
+      <c r="A100" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F100" s="5"/>
       <c r="G100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="3"/>
+      <c r="A101" s="1" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F101" s="5"/>
       <c r="G101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3"/>
+      <c r="A102" s="1" t="n">
+        <v>46345</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F102" s="5"/>
       <c r="G102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="3"/>
+      <c r="A103" s="1" t="n">
+        <v>46359</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F103" s="5"/>
       <c r="G103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3"/>
+      <c r="A104" s="1" t="n">
+        <v>46373</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="F104" s="5"/>
       <c r="G104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="3"/>
+      <c r="A105" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="F105" s="5"/>
       <c r="G105" s="6"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3"/>
+      <c r="A106" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F106" s="5"/>
       <c r="G106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="3"/>
+      <c r="A107" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="F107" s="5"/>
       <c r="G107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3"/>
+      <c r="A108" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="F108" s="5"/>
       <c r="G108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="3"/>
+      <c r="A109" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F109" s="5"/>
       <c r="G109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3"/>
+      <c r="A110" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F110" s="5"/>
       <c r="G110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3"/>
+      <c r="A111" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="F111" s="5"/>
       <c r="G111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3"/>
+      <c r="A112" s="1" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="F112" s="5"/>
       <c r="G112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="3"/>
+      <c r="A113" s="1" t="n">
+        <v>46360</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="F113" s="5"/>
       <c r="G113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3"/>
+      <c r="A114" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F114" s="5"/>
       <c r="G114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3"/>
+      <c r="A115" s="1" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F115" s="5"/>
       <c r="G115" s="6"/>
+      <c r="K115" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3"/>
+      <c r="A116" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="F116" s="5"/>
       <c r="G116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="3"/>
+      <c r="A117" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="F117" s="5"/>
       <c r="G117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3"/>
+      <c r="A118" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F118" s="5"/>
       <c r="G118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="3"/>
+      <c r="A119" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="F119" s="5"/>
       <c r="G119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3"/>
+      <c r="A120" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="F120" s="5"/>
       <c r="G120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="3"/>
+      <c r="A121" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="F121" s="5"/>
       <c r="G121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3"/>
+      <c r="A122" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="F122" s="5"/>
       <c r="G122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3"/>
+      <c r="A123" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F123" s="5"/>
       <c r="G123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3"/>
+      <c r="A124" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F124" s="5"/>
       <c r="G124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="3"/>
+      <c r="A125" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="F125" s="5"/>
       <c r="G125" s="6"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3"/>
+      <c r="A126" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="F126" s="5"/>
       <c r="G126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="3"/>
+      <c r="A127" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="F127" s="5"/>
       <c r="G127" s="6"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3"/>
+      <c r="A128" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="F128" s="5"/>
       <c r="G128" s="6"/>
+      <c r="K128" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="3"/>
+      <c r="A129" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="F129" s="5"/>
       <c r="G129" s="6"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3"/>
+      <c r="A130" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F130" s="5"/>
       <c r="G130" s="6"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3"/>
+      <c r="A131" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="F131" s="5"/>
       <c r="G131" s="6"/>
+      <c r="K131" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3"/>
+      <c r="A132" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="F132" s="5"/>
       <c r="G132" s="6"/>
+      <c r="K132" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3"/>
+      <c r="A133" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="F133" s="5"/>
       <c r="G133" s="6"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3"/>
+      <c r="A134" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="F134" s="5"/>
       <c r="G134" s="6"/>
+      <c r="K134" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="3"/>
+      <c r="A135" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F135" s="5"/>
       <c r="G135" s="6"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3"/>
+      <c r="A136" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="F136" s="5"/>
       <c r="G136" s="6"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="3"/>
+      <c r="A137" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="F137" s="5"/>
       <c r="G137" s="6"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3"/>
+      <c r="A138" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F138" s="5"/>
       <c r="G138" s="6"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="3"/>
+      <c r="A139" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="F139" s="5"/>
       <c r="G139" s="6"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3"/>
+      <c r="A140" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="F140" s="5"/>
       <c r="G140" s="6"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3"/>
+      <c r="A141" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F141" s="5"/>
       <c r="G141" s="6"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3"/>
+      <c r="A142" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="F142" s="5"/>
       <c r="G142" s="6"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="3"/>
+      <c r="A143" s="1" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F143" s="5"/>
       <c r="G143" s="6"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3"/>
+      <c r="A144" s="1" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="F144" s="5"/>
       <c r="G144" s="6"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="3"/>
+      <c r="A145" s="1" t="n">
+        <v>46345</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="F145" s="5"/>
       <c r="G145" s="6"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3"/>
+      <c r="A146" s="1" t="n">
+        <v>46359</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="F146" s="5"/>
       <c r="G146" s="6"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="3"/>
+      <c r="A147" s="1" t="n">
+        <v>46366</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="F147" s="5"/>
       <c r="G147" s="6"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="3"/>
+      <c r="A148" s="1" t="n">
+        <v>46373</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="F148" s="5"/>
       <c r="G148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3"/>
+      <c r="A149" s="1" t="n">
+        <v>46387</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="F149" s="5"/>
       <c r="G149" s="6"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3"/>
+      <c r="A150" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F150" s="5"/>
       <c r="G150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3"/>
+      <c r="A151" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F151" s="5"/>
       <c r="G151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="3"/>
+      <c r="A152" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F152" s="5"/>
       <c r="G152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3"/>
+      <c r="A153" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F153" s="5"/>
       <c r="G153" s="6"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="3"/>
+      <c r="A154" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F154" s="5"/>
       <c r="G154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3"/>
+      <c r="A155" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F155" s="5"/>
       <c r="G155" s="6"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="3"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="6"/>
+      <c r="A156" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.479166666666667</v>
+      </c>
+      <c r="G156" s="6" t="n">
+        <v>0.645833333333333</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="3"/>
+      <c r="A157" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F157" s="5"/>
       <c r="G157" s="6"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3"/>
+      <c r="A158" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F158" s="5"/>
       <c r="G158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3"/>
+      <c r="A159" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F159" s="5"/>
       <c r="G159" s="6"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="3"/>
+      <c r="A160" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F160" s="5"/>
       <c r="G160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3"/>
+      <c r="A161" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F161" s="5"/>
       <c r="G161" s="6"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="3"/>
+      <c r="A162" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F162" s="5"/>
       <c r="G162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3"/>
+      <c r="A163" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F163" s="5"/>
       <c r="G163" s="6"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="3"/>
+      <c r="A164" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F164" s="5"/>
       <c r="G164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3"/>
+      <c r="A165" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F165" s="5"/>
       <c r="G165" s="6"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="3"/>
+      <c r="A166" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F166" s="5"/>
       <c r="G166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3"/>
+      <c r="A167" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E167" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="F167" s="5"/>
       <c r="G167" s="6"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="3"/>
+      <c r="A168" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F168" s="5"/>
       <c r="G168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3"/>
+      <c r="A169" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F169" s="5"/>
       <c r="G169" s="6"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="3"/>
+      <c r="A170" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F170" s="5"/>
       <c r="G170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3"/>
+      <c r="A171" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F171" s="5"/>
       <c r="G171" s="6"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="3"/>
+      <c r="A172" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F172" s="5"/>
       <c r="G172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3"/>
+      <c r="A173" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="F173" s="5"/>
       <c r="G173" s="6"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="3"/>
+      <c r="A174" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F174" s="5"/>
       <c r="G174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3"/>
+      <c r="A175" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="F175" s="5"/>
       <c r="G175" s="6"/>
+      <c r="K175" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3"/>
+      <c r="A176" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="F176" s="5"/>
       <c r="G176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3"/>
+      <c r="A177" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="F177" s="5"/>
       <c r="G177" s="6"/>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="3"/>
+      <c r="A178" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="F178" s="5"/>
       <c r="G178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3"/>
+      <c r="A179" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="F179" s="5"/>
       <c r="G179" s="6"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="3"/>
+      <c r="A180" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F180" s="5"/>
       <c r="G180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3"/>
+      <c r="A181" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="F181" s="5"/>
       <c r="G181" s="6"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="3"/>
+      <c r="A182" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="F182" s="5"/>
       <c r="G182" s="6"/>
+      <c r="K182" s="4" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3"/>
+      <c r="A183" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F183" s="5"/>
       <c r="G183" s="6"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="3"/>
-      <c r="F184" s="5"/>
-      <c r="G184" s="6"/>
+      <c r="A184" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="G184" s="6" t="n">
+        <v>0.6875</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3"/>
+      <c r="A185" s="1" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="F185" s="5"/>
       <c r="G185" s="6"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="3"/>
+      <c r="A186" s="1" t="n">
+        <v>46346</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="F186" s="5"/>
       <c r="G186" s="6"/>
+      <c r="K186" s="4" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3"/>
+      <c r="A187" s="1" t="n">
+        <v>46360</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="F187" s="5"/>
       <c r="G187" s="6"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="3"/>
+      <c r="A188" s="1" t="n">
+        <v>46374</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F188" s="5"/>
       <c r="G188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3"/>
+      <c r="A189" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="F189" s="5"/>
       <c r="G189" s="6"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="3"/>
+      <c r="A190" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="F190" s="5"/>
       <c r="G190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="3"/>
+      <c r="A191" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="F191" s="5"/>
       <c r="G191" s="6"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3"/>
+      <c r="A192" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="F192" s="5"/>
       <c r="G192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="3"/>
+      <c r="A193" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="F193" s="5"/>
       <c r="G193" s="6"/>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3"/>
+      <c r="A194" s="1" t="n">
+        <v>46334</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="F194" s="5"/>
       <c r="G194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="3"/>
+      <c r="A195" s="1" t="n">
+        <v>46369</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="F195" s="5"/>
       <c r="G195" s="6"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3"/>
+      <c r="A196" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="F196" s="5"/>
       <c r="G196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="3"/>
+      <c r="A197" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="F197" s="5"/>
       <c r="G197" s="6"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="6"/>
+      <c r="A198" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="G198" s="6" t="n">
+        <v>0.6875</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="3"/>
+      <c r="A199" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F199" s="5"/>
       <c r="G199" s="6"/>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3"/>
+      <c r="A200" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F200" s="5"/>
       <c r="G200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="3"/>
+      <c r="A201" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="F201" s="5"/>
       <c r="G201" s="6"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3"/>
+      <c r="A202" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="F202" s="5"/>
       <c r="G202" s="6"/>
+      <c r="I202" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="6"/>
+      <c r="A203" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G203" s="6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3"/>
+      <c r="A204" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="F204" s="5"/>
       <c r="G204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="3"/>
+      <c r="A205" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="F205" s="5"/>
       <c r="G205" s="6"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3"/>
+      <c r="A206" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="F206" s="5"/>
       <c r="G206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="3"/>
+      <c r="A207" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="F207" s="5"/>
       <c r="G207" s="6"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="3"/>
+      <c r="A208" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="F208" s="5"/>
       <c r="G208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3"/>
+      <c r="A209" s="1" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="F209" s="5"/>
       <c r="G209" s="6"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="3"/>
+      <c r="A210" s="1" t="n">
+        <v>46347</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="F210" s="5"/>
       <c r="G210" s="6"/>
+      <c r="I210" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3"/>
+      <c r="A211" s="1" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="F211" s="5"/>
       <c r="G211" s="6"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="6"/>
+      <c r="A212" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F212" s="2"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="6"/>
+      <c r="A213" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F213" s="2"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="3"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="6"/>
+      <c r="A214" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F214" s="2"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="6"/>
+      <c r="A215" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F215" s="2"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="3"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="6"/>
+      <c r="A216" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F216" s="2"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="6"/>
+      <c r="A217" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F217" s="2"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="3"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="6"/>
+      <c r="A218" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F218" s="2"/>
+      <c r="I218" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="6"/>
+      <c r="A219" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F219" s="2"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="3"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="6"/>
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F220" s="2"/>
+      <c r="I220" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="6"/>
+      <c r="A221" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F221" s="2"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="3"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="6"/>
+      <c r="A222" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F222" s="2"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="6"/>
+      <c r="A223" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F223" s="2"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="6"/>
+      <c r="A224" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F224" s="2"/>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3"/>
-      <c r="F225" s="5"/>
-      <c r="G225" s="6"/>
+      <c r="A225" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F225" s="2"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="6"/>
+      <c r="A226" s="1" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F226" s="2"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="6"/>
+      <c r="A227" s="1" t="n">
+        <v>46364</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F227" s="2"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="6"/>
+      <c r="A228" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D228" s="7"/>
+      <c r="F228" s="2"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3"/>
-      <c r="F229" s="5"/>
-      <c r="G229" s="6"/>
+      <c r="A229" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F229" s="2"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="6"/>
+      <c r="A230" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F230" s="2"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="3"/>
-      <c r="F231" s="5"/>
-      <c r="G231" s="6"/>
+      <c r="A231" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F231" s="2"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3"/>
-      <c r="F232" s="5"/>
-      <c r="G232" s="6"/>
+      <c r="A232" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D232" s="7"/>
+      <c r="F232" s="2"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="3"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="6"/>
+      <c r="A233" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D233" s="7"/>
+      <c r="F233" s="2"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3"/>
-      <c r="F234" s="5"/>
-      <c r="G234" s="6"/>
+      <c r="A234" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D234" s="7"/>
+      <c r="F234" s="2"/>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="3"/>
-      <c r="F235" s="5"/>
-      <c r="G235" s="6"/>
+      <c r="A235" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235" s="7"/>
+      <c r="F235" s="2"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3"/>
-      <c r="F236" s="5"/>
-      <c r="G236" s="6"/>
+      <c r="A236" s="1" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D236" s="7"/>
+      <c r="F236" s="2"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="3"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="6"/>
+      <c r="A237" s="1" t="n">
+        <v>46367</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D237" s="7"/>
+      <c r="F237" s="2"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="6"/>
+      <c r="A238" s="1" t="n">
+        <v>46395</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C238" s="7"/>
+      <c r="D238" s="7"/>
+      <c r="F238" s="2"/>
+      <c r="I238" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="3"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="6"/>
+      <c r="A239" s="1" t="n">
+        <v>46409</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D239" s="7"/>
+      <c r="F239" s="2"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3"/>
-      <c r="F240" s="5"/>
-      <c r="G240" s="6"/>
+      <c r="A240" s="1" t="n">
+        <v>46430</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D240" s="7"/>
+      <c r="F240" s="2"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="3"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="6"/>
+      <c r="A241" s="1" t="n">
+        <v>46444</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D241" s="7"/>
+      <c r="F241" s="2"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3"/>
-      <c r="F242" s="5"/>
-      <c r="G242" s="6"/>
+      <c r="A242" s="1" t="n">
+        <v>46458</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D242" s="7"/>
+      <c r="F242" s="2"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="3"/>
-      <c r="F243" s="5"/>
-      <c r="G243" s="6"/>
+      <c r="A243" s="1" t="n">
+        <v>46486</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D243" s="7"/>
+      <c r="F243" s="2"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3"/>
-      <c r="F244" s="5"/>
-      <c r="G244" s="6"/>
+      <c r="A244" s="1" t="n">
+        <v>46500</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D244" s="7"/>
+      <c r="F244" s="2"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="3"/>
-      <c r="F245" s="5"/>
-      <c r="G245" s="6"/>
+      <c r="A245" s="1" t="n">
+        <v>46521</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D245" s="7"/>
+      <c r="F245" s="2"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3"/>
-      <c r="F246" s="5"/>
-      <c r="G246" s="6"/>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
+      <c r="D246" s="7"/>
+      <c r="F246" s="2"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="3"/>
-      <c r="F247" s="5"/>
-      <c r="G247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7"/>
+      <c r="F247" s="2"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3"/>
-      <c r="F248" s="5"/>
-      <c r="G248" s="6"/>
+      <c r="B248" s="7"/>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7"/>
+      <c r="F248" s="2"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="3"/>
       <c r="F249" s="5"/>
       <c r="G249" s="6"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3"/>
       <c r="F250" s="5"/>
       <c r="G250" s="6"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="3"/>
       <c r="F251" s="5"/>
       <c r="G251" s="6"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3"/>
       <c r="F252" s="5"/>
       <c r="G252" s="6"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="3"/>
       <c r="F253" s="5"/>
       <c r="G253" s="6"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3"/>
       <c r="F254" s="5"/>
       <c r="G254" s="6"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="3"/>
       <c r="F255" s="5"/>
       <c r="G255" s="6"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3"/>
       <c r="F256" s="5"/>
       <c r="G256" s="6"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="3"/>
       <c r="F257" s="5"/>
       <c r="G257" s="6"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3"/>
       <c r="F258" s="5"/>
       <c r="G258" s="6"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="3"/>
       <c r="F259" s="5"/>
       <c r="G259" s="6"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3"/>
       <c r="F260" s="5"/>
       <c r="G260" s="6"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="3"/>
       <c r="F261" s="5"/>
       <c r="G261" s="6"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3"/>
       <c r="F262" s="5"/>
       <c r="G262" s="6"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="3"/>
       <c r="F263" s="5"/>
       <c r="G263" s="6"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3"/>
       <c r="F264" s="5"/>
       <c r="G264" s="6"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="3"/>
       <c r="F265" s="5"/>
       <c r="G265" s="6"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3"/>
       <c r="F266" s="5"/>
       <c r="G266" s="6"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="3"/>
       <c r="F267" s="5"/>
       <c r="G267" s="6"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3"/>
       <c r="F268" s="5"/>
       <c r="G268" s="6"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="3"/>
       <c r="F269" s="5"/>
       <c r="G269" s="6"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3"/>
       <c r="F270" s="5"/>
       <c r="G270" s="6"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="3"/>
       <c r="F271" s="5"/>
       <c r="G271" s="6"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3"/>
       <c r="F272" s="5"/>
       <c r="G272" s="6"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3"/>
       <c r="F273" s="5"/>
       <c r="G273" s="6"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="3"/>
       <c r="F274" s="5"/>
       <c r="G274" s="6"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3"/>
       <c r="F275" s="5"/>
       <c r="G275" s="6"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="3"/>
       <c r="F276" s="5"/>
       <c r="G276" s="6"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3"/>
       <c r="F277" s="5"/>
       <c r="G277" s="6"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="3"/>
       <c r="F278" s="5"/>
       <c r="G278" s="6"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3"/>
       <c r="F279" s="5"/>
       <c r="G279" s="6"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="3"/>
       <c r="F280" s="5"/>
       <c r="G280" s="6"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3"/>
       <c r="F281" s="5"/>
       <c r="G281" s="6"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="3"/>
       <c r="F282" s="5"/>
       <c r="G282" s="6"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3"/>
       <c r="F283" s="5"/>
       <c r="G283" s="6"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="3"/>
       <c r="F284" s="5"/>
       <c r="G284" s="6"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="3"/>
       <c r="F285" s="5"/>
       <c r="G285" s="6"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="3"/>
       <c r="F286" s="5"/>
       <c r="G286" s="6"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F287" s="5"/>
       <c r="G287" s="6"/>
-    </row>
-    <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F288" s="5"/>
-      <c r="G288" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
